--- a/Results/Study 1/VGG16 (pretrained)/Confusion Matrices.xlsx
+++ b/Results/Study 1/VGG16 (pretrained)/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>380</v>
+        <v>585</v>
       </c>
       <c r="C2">
-        <v>260</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="C3">
-        <v>444</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -440,10 +440,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="C2">
-        <v>53</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -451,10 +451,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C3">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
